--- a/vlearn-app/public/quiz_excel/Day_15_Triển khai thực tế _ Định hướng Enterprise/Day_15_Phan_02_23_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_15_Triển khai thực tế _ Định hướng Enterprise/Day_15_Phan_02_23_Cau.xlsx
@@ -747,7 +747,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,5</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
@@ -756,7 +756,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một posting gần tên chưa chắc cùng population tuyển dụng.</t>
+          <t>Để so sánh yêu cầu tuyển dụng Data Engineer cấp độ Junior tại Việt Nam trong quý hiện tại, chỉ lấy các bài đăng đúng nhóm đối tượng: (a) Junior Data Engineer tại TP.HCM đăng 2 tuần trước, (b) Junior Data Engineer tại Hà Nội đăng 1 tháng trước, (e) Junior Data Engineer làm remote tại Việt Nam đăng 3 tuần trước.</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I10" s="4" t="n">
@@ -1025,7 +1025,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ dùng invariant input, chưa dùng search/route feasibility.</t>
+          <t>Dữ liệu đầu vào vi phạm tính toàn vẹn phải bị loại ngay trước khi chạy thuật toán routing: (a) Thông số vận tốc dùng chung bị xung đột giữa các dòng (0,8 vs 1,0), (b) trùng lặp order_id trong cùng một instance, (c) giá trị nhu cầu không phải là số hợp lệ ('abc').</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1073,7 +1073,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính distance trước rồi chia đúng unit km/phút.</t>
+          <t>Khoảng cách Euclidean từ depot (0,0) tới order (3,4): sqrt(3^2 + 4^2) = sqrt(9 + 16) = 5 km. Thời gian di chuyển với vận tốc 0,5 km/phút: 5 km / 0,5 km/phút = 10 phút.</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1121,7 +1121,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Departure A không bằng arrival A khi có wait/service.</t>
+          <t>Arrival tại A = 4; Ready time A = 10; Service time = 3; Leg A-&gt;B = 2. Do xe đến trước ready time nên phải chờ đến t=10 mới bắt đầu service. Service hoàn tất lúc 10 + 3 = 13. Thời điểm arrival tại B = 13 + 2 = 15.</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1169,7 +1169,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Áp max(0, arrival−due) cho từng order rồi cộng.</t>
+          <t>Lateness từng order: Order A = max(0, 12 - 10) = 2; Order B = max(0, 8 - 9) = 0; Order C = max(0, 20 - 14) = 6. Tổng lateness = 2 + 0 + 6 = 8 phút.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1217,7 +1217,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính max(0,arrival−due) từng order rồi lấy max.</t>
+          <t>Lateness của 4 orders: Order 1: max(0, 9-10)=0; Order 2: max(0, 15-11)=4; Order 3: max(0, 22-18)=4; Order 4: max(0, 30-31)=0. Maximum lateness = max(0, 4, 4, 0) = 4 phút.</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1265,7 +1265,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Overtime chỉ biết sau khi cộng return leg.</t>
+          <t>Hoàn tất service đơn cuối tại t=52; quay về depot mất 11 phút =&gt; Xe về tới depot lúc 52 + 11 = 63. Shift end = 60 =&gt; Overtime = max(0, 63 - 60) = 3 phút.</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1313,7 +1313,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đừng bắt đầu return leg từ arrival trước service.</t>
+          <t>Đơn cuối arrival lúc t=40, service 8 phút =&gt; Hoàn tất lúc 40 + 8 = 48. Chặng về depot mất 7 phút =&gt; Về depot lúc 48 + 7 = 55. Shift end = 52 =&gt; Overtime = max(0, 55 - 52) = 3 phút.</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Placeholder rỗng không tính xe.</t>
+          <t>Dung lượng fleet num_vehicles=2. Solution có cấu trúc `[[], [1,2], [], [3]]`. Các mảng rỗng `[]` là placeholder; chỉ có hai route không rỗng là `[1,2]` và `[3]` đại diện cho 2 xe thực sự được sử dụng.</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I22" s="4" t="n">
@@ -1620,7 +1620,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So từng dimension trước, chỉ kết luận overall nếu objective được khai báo.</t>
+          <t>So sánh hai lời giải đa mục tiêu khi chưa biết trọng số: (a) B có tổng quãng đường tốt hơn (90 &lt; 100), (b) A dùng ít xe hơn (2 &lt; 3) và trễ giờ ít hơn (5 &lt; 12), (c) không thể kết luận giải pháp nào tối ưu tổng thể nếu chưa có trọng số chính thức, (e) hai lời giải ngang nhau về làm thêm giờ (0) và đơn hàng chưa phục vụ (0).</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1716,7 +1716,7 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính ratio trước rồi áp cap; invalid/missing mới nhận zero.</t>
+          <t>Raw score = 100 * (reference cost / team cost) = 100 * (120 / 60) = 200. Áp dụng trần cap=150: min(150, 200) = 150 điểm.</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1764,7 +1764,7 @@
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cap chỉ tác động khi raw ratio vượt 150.</t>
+          <t>Raw score = 100 * (reference cost / team cost) = 100 * (80 / 100) = 80. Áp dụng cap=150: min(150, 80) = 80 điểm.</t>
         </is>
       </c>
     </row>
